--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40044452-376D-4592-A232-914F8BAADE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F5BB8E-EC0D-4C7D-924C-93120E3BC0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
+    <sheet name="Nr2_Jan19" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3287" uniqueCount="1540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="1702">
   <si>
     <t>Imprint</t>
   </si>
@@ -4645,6 +4646,492 @@
   </si>
   <si>
     <t>https://www.magonlinelibrary.com/journal/llwc</t>
+  </si>
+  <si>
+    <t>MDPI</t>
+  </si>
+  <si>
+    <t>2673-4931</t>
+  </si>
+  <si>
+    <t>Environmental Sciences Proceedings</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/environsciproc</t>
+  </si>
+  <si>
+    <t>3042-6618</t>
+  </si>
+  <si>
+    <t>Accounting and Auditing</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/accountaudit</t>
+  </si>
+  <si>
+    <t>3042-6081</t>
+  </si>
+  <si>
+    <t>Adhesives</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/adhesives</t>
+  </si>
+  <si>
+    <t>3042-6723</t>
+  </si>
+  <si>
+    <t>AI Chemistry</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aichem</t>
+  </si>
+  <si>
+    <t>3042-8831</t>
+  </si>
+  <si>
+    <t>AI for Engineering</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aieng</t>
+  </si>
+  <si>
+    <t>3042-8130</t>
+  </si>
+  <si>
+    <t>AI in Education</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aieduc</t>
+  </si>
+  <si>
+    <t>3042-6707</t>
+  </si>
+  <si>
+    <t>AI in Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aimed</t>
+  </si>
+  <si>
+    <t>3042-6715</t>
+  </si>
+  <si>
+    <t>AI Materials</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aimater</t>
+  </si>
+  <si>
+    <t>3042-5999</t>
+  </si>
+  <si>
+    <t>AI Sensors</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aisens</t>
+  </si>
+  <si>
+    <t>3042-8491</t>
+  </si>
+  <si>
+    <t>Analog</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/analog</t>
+  </si>
+  <si>
+    <t>3042-6553</t>
+  </si>
+  <si>
+    <t>AppliedPhys</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/appliedphys</t>
+  </si>
+  <si>
+    <t>3042-7576</t>
+  </si>
+  <si>
+    <t>Astronautics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/astronautics</t>
+  </si>
+  <si>
+    <t>3042-8092</t>
+  </si>
+  <si>
+    <t>Bioresources and Bioproducts</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/bioresourbioprod</t>
+  </si>
+  <si>
+    <t>3042-6111</t>
+  </si>
+  <si>
+    <t>Biosphere</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/biosphere</t>
+  </si>
+  <si>
+    <t>1664-204X</t>
+  </si>
+  <si>
+    <t>Cardiovascular Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/cardiovascmed</t>
+  </si>
+  <si>
+    <t>3042-5158</t>
+  </si>
+  <si>
+    <t>Clinical Bioenergetics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/clinbioenerg</t>
+  </si>
+  <si>
+    <t>3042-6448</t>
+  </si>
+  <si>
+    <t>Complexities</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/complexities</t>
+  </si>
+  <si>
+    <t>1943-3883</t>
+  </si>
+  <si>
+    <t>Craniomaxillofacial Trauma &amp; Reconstruction</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/cmtr</t>
+  </si>
+  <si>
+    <t>3042-8165</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/culture</t>
+  </si>
+  <si>
+    <t>3042-7592</t>
+  </si>
+  <si>
+    <t>Entropic and Disordered Matter</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/edm</t>
+  </si>
+  <si>
+    <t>3042-5743</t>
+  </si>
+  <si>
+    <t>Environmental and Earth Sciences Proceedings</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/eesp</t>
+  </si>
+  <si>
+    <t>3042-6693</t>
+  </si>
+  <si>
+    <t>Family Sciences</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/famsci</t>
+  </si>
+  <si>
+    <t>2248-2997</t>
+  </si>
+  <si>
+    <t>GERMS</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/germs</t>
+  </si>
+  <si>
+    <t>3042-5832</t>
+  </si>
+  <si>
+    <t>Green Health</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/greenhealth</t>
+  </si>
+  <si>
+    <t>3042-8432</t>
+  </si>
+  <si>
+    <t>Hydropower</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/hydropower</t>
+  </si>
+  <si>
+    <t>3042-8084</t>
+  </si>
+  <si>
+    <t>International Journal of Cognitive Sciences</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijcs</t>
+  </si>
+  <si>
+    <t>3042-7681</t>
+  </si>
+  <si>
+    <t>International Journal of Environmental Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijem</t>
+  </si>
+  <si>
+    <t>2694-2526</t>
+  </si>
+  <si>
+    <t>International Journal of Orofacial Myology and Myofunctional Therapy</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijom</t>
+  </si>
+  <si>
+    <t>3042-6774</t>
+  </si>
+  <si>
+    <t>Journal of Aesthetic Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jaestheticmed</t>
+  </si>
+  <si>
+    <t>3042-6987</t>
+  </si>
+  <si>
+    <t>Journal of CardioRenal Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jcrm</t>
+  </si>
+  <si>
+    <t>1995-8692</t>
+  </si>
+  <si>
+    <t>Journal of Eye Movement Research</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jemr</t>
+  </si>
+  <si>
+    <t>2392-7674</t>
+  </si>
+  <si>
+    <t>Journal of Mind and Medical Sciences</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jmms</t>
+  </si>
+  <si>
+    <t>3042-5689</t>
+  </si>
+  <si>
+    <t>Journal of Parks</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jop</t>
+  </si>
+  <si>
+    <t>3042-7886</t>
+  </si>
+  <si>
+    <t>Lights</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/lights</t>
+  </si>
+  <si>
+    <t>3042-5344</t>
+  </si>
+  <si>
+    <t>Microelectronics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/microelectronics</t>
+  </si>
+  <si>
+    <t>3042-5697</t>
+  </si>
+  <si>
+    <t>Microwave</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/microwave</t>
+  </si>
+  <si>
+    <t>3042-5034</t>
+  </si>
+  <si>
+    <t>Modern Mathematical Physics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/mmphys</t>
+  </si>
+  <si>
+    <t>3042-6308</t>
+  </si>
+  <si>
+    <t>Multimedia</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/multimedia</t>
+  </si>
+  <si>
+    <t>3042-8807</t>
+  </si>
+  <si>
+    <t>Neuroimaging</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/neuroimaging</t>
+  </si>
+  <si>
+    <t>3042-8637</t>
+  </si>
+  <si>
+    <t>Occupational Health</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/occuphealth</t>
+  </si>
+  <si>
+    <t>3042-6529</t>
+  </si>
+  <si>
+    <t>Peace Studies</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/peacestud</t>
+  </si>
+  <si>
+    <t>3042-7614</t>
+  </si>
+  <si>
+    <t>Precision Oncology</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/precisoncol</t>
+  </si>
+  <si>
+    <t>3042-6197</t>
+  </si>
+  <si>
+    <t>Purification</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/purification</t>
+  </si>
+  <si>
+    <t>3091-101X</t>
+  </si>
+  <si>
+    <t>Romanian Journal of Preventive Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/rjpm</t>
+  </si>
+  <si>
+    <t>3042-9013</t>
+  </si>
+  <si>
+    <t>Semiconductors and Heterogeneous Integration</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/shi</t>
+  </si>
+  <si>
+    <t>3042-7126</t>
+  </si>
+  <si>
+    <t>Theoretical and Applied Ergonomics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/tae</t>
+  </si>
+  <si>
+    <t>3042-8629</t>
+  </si>
+  <si>
+    <t>Journal of Innovation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/joi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-9250 </t>
+  </si>
+  <si>
+    <t>Journal of Phytomedicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jphytomed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-934X </t>
+  </si>
+  <si>
+    <t>Low-altitude Economy</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/lae</t>
+  </si>
+  <si>
+    <t>3042-8181</t>
+  </si>
+  <si>
+    <t>Trends in Public Health</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/tph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-884X </t>
+  </si>
+  <si>
+    <t>Stratigraphy and Sedimentology</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/stratsediment</t>
+  </si>
+  <si>
+    <t>Frontiers</t>
+  </si>
+  <si>
+    <t>2813-6187</t>
+  </si>
+  <si>
+    <t>Frontiers in Complex Systems</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/complex-systems</t>
+  </si>
+  <si>
+    <t>2634-730X</t>
+  </si>
+  <si>
+    <t>Earth Science Systems and Society</t>
+  </si>
+  <si>
+    <t>https://www.escubed.org/journals/earth-science-systems-and-society</t>
+  </si>
+  <si>
+    <t>dubblett borttagen</t>
   </si>
 </sst>
 </file>
@@ -15724,4 +16211,1259 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1D323B-A6AD-4330-BC48-B16F75806926}">
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>555</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F5BB8E-EC0D-4C7D-924C-93120E3BC0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595DEB9B-B058-4A68-9813-D30C73D92CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
     <sheet name="Nr2_Jan19" sheetId="2" r:id="rId2"/>
+    <sheet name="Nr3_Jan20" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="1702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3688" uniqueCount="1709">
   <si>
     <t>Imprint</t>
   </si>
@@ -5132,6 +5133,27 @@
   </si>
   <si>
     <t>dubblett borttagen</t>
+  </si>
+  <si>
+    <t>2631-4940</t>
+  </si>
+  <si>
+    <t>BMJ Surgery, Interventions, &amp; Health Technologies</t>
+  </si>
+  <si>
+    <t>https://sit.bmj.com/</t>
+  </si>
+  <si>
+    <t>2978-1809</t>
+  </si>
+  <si>
+    <t>BMJ Connections Surgery</t>
+  </si>
+  <si>
+    <t>https://connectionssurgery.bmj.com/</t>
+  </si>
+  <si>
+    <t>ny</t>
   </si>
 </sst>
 </file>
@@ -17466,4 +17488,86 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A182B91-835E-4E83-B5C7-A60B1DA82CFC}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595DEB9B-B058-4A68-9813-D30C73D92CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8169E96-4C60-462E-ADAE-88E463E82EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
     <sheet name="Nr2_Jan19" sheetId="2" r:id="rId2"/>
-    <sheet name="Nr3_Jan20" sheetId="3" r:id="rId3"/>
+    <sheet name="Rättningar_Jan20" sheetId="3" r:id="rId3"/>
+    <sheet name="Nr3_Feb16" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3688" uniqueCount="1709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4673" uniqueCount="2037">
   <si>
     <t>Imprint</t>
   </si>
@@ -5154,6 +5155,990 @@
   </si>
   <si>
     <t>ny</t>
+  </si>
+  <si>
+    <t>Academic Medicine</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/academicmedicine</t>
+  </si>
+  <si>
+    <t>1535-4970</t>
+  </si>
+  <si>
+    <t>American Journal of Respiratory and Critical Care Medicine</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/ajrccm</t>
+  </si>
+  <si>
+    <t>2325-6621</t>
+  </si>
+  <si>
+    <t>Annals of the American Thoracic Society</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/annalsats</t>
+  </si>
+  <si>
+    <t>2690-7097</t>
+  </si>
+  <si>
+    <t>ATS Scholar</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/atsscholar</t>
+  </si>
+  <si>
+    <t>1365-2168</t>
+  </si>
+  <si>
+    <t>ISSN 0007-1323</t>
+  </si>
+  <si>
+    <t>BJS: British Journal of Surgery</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/bjs</t>
+  </si>
+  <si>
+    <t>ändrar titelnamnet, lägger till BJS</t>
+  </si>
+  <si>
+    <t>oxford University Press</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/chidev</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/cdpers</t>
+  </si>
+  <si>
+    <t>Composite Design and Manufacturing</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/cdm</t>
+  </si>
+  <si>
+    <t>2044-8422</t>
+  </si>
+  <si>
+    <t>Current Legal Problems</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/clp</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/eschf</t>
+  </si>
+  <si>
+    <t>2977-8565</t>
+  </si>
+  <si>
+    <t>European Heart Journal – Valvular and Structural Heart Disease</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/ehjvshd</t>
+  </si>
+  <si>
+    <t>European Journal of Heart Failure</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/eurjhf</t>
+  </si>
+  <si>
+    <t>2396-9881</t>
+  </si>
+  <si>
+    <t>European Stroke Journal</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/esj</t>
+  </si>
+  <si>
+    <t>2471-1411</t>
+  </si>
+  <si>
+    <t>Forensic Sciences Research</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/fsr</t>
+  </si>
+  <si>
+    <t>2633-8823</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/function</t>
+  </si>
+  <si>
+    <t>2977-7496</t>
+  </si>
+  <si>
+    <t>Global Perspectives in Communication</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/gpc</t>
+  </si>
+  <si>
+    <t>2977-7488</t>
+  </si>
+  <si>
+    <t>Global Perspectives on Nutrition</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/gpn</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/joneph</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/jvim</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/molecular-omics</t>
+  </si>
+  <si>
+    <t>Monographs of the Society for Research in Child Development</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/srcdmo</t>
+  </si>
+  <si>
+    <t>2977-4454</t>
+  </si>
+  <si>
+    <t>Neuro-Oncology Pediatrics</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/neuro-onc-peds</t>
+  </si>
+  <si>
+    <t>1741-7899</t>
+  </si>
+  <si>
+    <t>Reproduction</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/reproduction</t>
+  </si>
+  <si>
+    <t>3049-5245</t>
+  </si>
+  <si>
+    <t>Research Connections</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/rescon</t>
+  </si>
+  <si>
+    <t>2976-8586</t>
+  </si>
+  <si>
+    <t>RSS Data Science and Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/rssdat</t>
+  </si>
+  <si>
+    <t>Korrigerar namnet</t>
+  </si>
+  <si>
+    <t>1460-3640</t>
+  </si>
+  <si>
+    <t>Security Dialogue</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/sd</t>
+  </si>
+  <si>
+    <t>1744-8581</t>
+  </si>
+  <si>
+    <t>The Library</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/library</t>
+  </si>
+  <si>
+    <t>Advances in Business and Management Research</t>
+  </si>
+  <si>
+    <t>Advances in Ophthalmology Practice and Research</t>
+  </si>
+  <si>
+    <t>Advances in Radiation Oncology</t>
+  </si>
+  <si>
+    <t>Annales de Paléontologie</t>
+  </si>
+  <si>
+    <t>Appetite: Disordered Eating</t>
+  </si>
+  <si>
+    <t>Applied Animal Science</t>
+  </si>
+  <si>
+    <t>Applied Biomolecules: Bioactive Materials</t>
+  </si>
+  <si>
+    <t>Applied Studies in Innovative Learning and Teaching</t>
+  </si>
+  <si>
+    <t>Archives of Rehabilitation Research and Clinical Translation</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in Emergency Medicine</t>
+  </si>
+  <si>
+    <t>Bacteriophage</t>
+  </si>
+  <si>
+    <t>Biomass Futures</t>
+  </si>
+  <si>
+    <t>Biomaterials and Living Medicine for Pharmaceutics</t>
+  </si>
+  <si>
+    <t>Cancer Neuroscience</t>
+  </si>
+  <si>
+    <t>Cell Death</t>
+  </si>
+  <si>
+    <t>Cell Insight</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Journal: Green and Sustainable</t>
+  </si>
+  <si>
+    <t>Chip</t>
+  </si>
+  <si>
+    <t>Cities: Smarter Futures</t>
+  </si>
+  <si>
+    <t>Cleaner Manufacturing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Climate Physics and Atmospheric Science: Scientific Insights and Societal Challenges </t>
+  </si>
+  <si>
+    <t>Clinical Dental Journal</t>
+  </si>
+  <si>
+    <t>Clinical Traditional Medicine and Pharmacology</t>
+  </si>
+  <si>
+    <t>Coacervates</t>
+  </si>
+  <si>
+    <t>Construction and Building Materials in Transportation</t>
+  </si>
+  <si>
+    <t>Crop and Environment</t>
+  </si>
+  <si>
+    <t>Disease and Therapeutics</t>
+  </si>
+  <si>
+    <t>EANM Innovation</t>
+  </si>
+  <si>
+    <t>Earth System</t>
+  </si>
+  <si>
+    <t>Environmental Management: Economics and Policy</t>
+  </si>
+  <si>
+    <t>Environmental Management: Emerging Contaminants</t>
+  </si>
+  <si>
+    <t>Environmental Management: Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Environmental Management: Smart Solutions</t>
+  </si>
+  <si>
+    <t>e-Prime – Nexus of Electrical, Electronic, and Intelligent Engineering</t>
+  </si>
+  <si>
+    <t>Farming System</t>
+  </si>
+  <si>
+    <t>Fermented Foods</t>
+  </si>
+  <si>
+    <t>Football Studies</t>
+  </si>
+  <si>
+    <t>Geriatric Nursing: Asia</t>
+  </si>
+  <si>
+    <t>Global Neurological Insights</t>
+  </si>
+  <si>
+    <t>Gut Microbiology</t>
+  </si>
+  <si>
+    <t>Gut Microbiome and Health</t>
+  </si>
+  <si>
+    <t>Health Policy in Asia</t>
+  </si>
+  <si>
+    <t>Heavy Rail</t>
+  </si>
+  <si>
+    <t>iLIVER</t>
+  </si>
+  <si>
+    <t>International Journal of Cardiology Innovations</t>
+  </si>
+  <si>
+    <t>iPharma</t>
+  </si>
+  <si>
+    <t>JAND Global Reports</t>
+  </si>
+  <si>
+    <t>JEM International</t>
+  </si>
+  <si>
+    <t>Jornal de Pediatria</t>
+  </si>
+  <si>
+    <t>Journal of Aquatic Plants</t>
+  </si>
+  <si>
+    <t>Journal of Biomechanics Open</t>
+  </si>
+  <si>
+    <t>Journal of Experimental Horticulture</t>
+  </si>
+  <si>
+    <t>Journal of Gastrointestinal Surgery Open</t>
+  </si>
+  <si>
+    <t>Journal of Hazardous Materials: Organics</t>
+  </si>
+  <si>
+    <t>Journal of Hazardous Materials: Plastics</t>
+  </si>
+  <si>
+    <t>Journal of Healthcare Quality Research</t>
+  </si>
+  <si>
+    <t>Journal of Intensive Medicine</t>
+  </si>
+  <si>
+    <t>Journal of Ocean Engineering and Science</t>
+  </si>
+  <si>
+    <t>Journal of Pyrogeography</t>
+  </si>
+  <si>
+    <t>Journal of Shoulder and Elbow Arthroplasty</t>
+  </si>
+  <si>
+    <t>Journal of Sports Medicine, Animal Rehabilitation and Physiotherapy</t>
+  </si>
+  <si>
+    <t>Kidney International Case Reports</t>
+  </si>
+  <si>
+    <t>L'Anthropologie</t>
+  </si>
+  <si>
+    <t>Marine Geoscience and Energy Resources </t>
+  </si>
+  <si>
+    <t>Molecular Therapy Advances</t>
+  </si>
+  <si>
+    <t>Mutation Research: Fundamental and Molecular Mechanisms of Mutagenesis</t>
+  </si>
+  <si>
+    <t>NeuroImage Stroke</t>
+  </si>
+  <si>
+    <t>Nutritional Psychiatry</t>
+  </si>
+  <si>
+    <t>Open Nuclear Energy</t>
+  </si>
+  <si>
+    <t>PEC Global</t>
+  </si>
+  <si>
+    <t>Periodontology Journal</t>
+  </si>
+  <si>
+    <t>Plant Research</t>
+  </si>
+  <si>
+    <t>Precision Pathology</t>
+  </si>
+  <si>
+    <t>Preventive Veterinary Medicine: Regional Studies and Reports</t>
+  </si>
+  <si>
+    <t>Progress in Solid State Chemistry</t>
+  </si>
+  <si>
+    <t>Pulmonary Function Diagnostics</t>
+  </si>
+  <si>
+    <t>Revista de Investigación Clínica</t>
+  </si>
+  <si>
+    <t>Strategic Business Research</t>
+  </si>
+  <si>
+    <t>Sustainable Cities and Society: Advances</t>
+  </si>
+  <si>
+    <t>Systems Ethnopharmacology and Sustainable Bioresources</t>
+  </si>
+  <si>
+    <t>The EANM Journal</t>
+  </si>
+  <si>
+    <t>The Lancet Regional Health - Africa</t>
+  </si>
+  <si>
+    <t>The Swine Journal</t>
+  </si>
+  <si>
+    <t>The Veterinary Journal: Pharmacology &amp; Toxicology</t>
+  </si>
+  <si>
+    <t>Transformative Energy</t>
+  </si>
+  <si>
+    <t>Transnational Mobilities</t>
+  </si>
+  <si>
+    <t>Transportation Research Today</t>
+  </si>
+  <si>
+    <t>Trends Open</t>
+  </si>
+  <si>
+    <t>Tribology and Interfaces</t>
+  </si>
+  <si>
+    <t>Urology Horizons</t>
+  </si>
+  <si>
+    <t>3051-0511</t>
+  </si>
+  <si>
+    <t>2667-3762</t>
+  </si>
+  <si>
+    <t>2452-1094</t>
+  </si>
+  <si>
+    <t>0753-3969</t>
+  </si>
+  <si>
+    <t>3117-3950</t>
+  </si>
+  <si>
+    <t>2590-2865</t>
+  </si>
+  <si>
+    <t>3117-5031</t>
+  </si>
+  <si>
+    <t>3051-3243</t>
+  </si>
+  <si>
+    <t>2590-1095</t>
+  </si>
+  <si>
+    <t>3051-2883</t>
+  </si>
+  <si>
+    <t>3051-2697</t>
+  </si>
+  <si>
+    <t>3051-4444</t>
+  </si>
+  <si>
+    <t>3117-4663</t>
+  </si>
+  <si>
+    <t>3051-3235</t>
+  </si>
+  <si>
+    <t>3051-1151</t>
+  </si>
+  <si>
+    <t>2772-8927</t>
+  </si>
+  <si>
+    <t>3051-0031</t>
+  </si>
+  <si>
+    <t>2709-4723</t>
+  </si>
+  <si>
+    <t>3117-3764</t>
+  </si>
+  <si>
+    <t>3050-998X</t>
+  </si>
+  <si>
+    <t>3051-4088</t>
+  </si>
+  <si>
+    <t>3117-4892</t>
+  </si>
+  <si>
+    <t>2097-3829</t>
+  </si>
+  <si>
+    <t>3117-6178</t>
+  </si>
+  <si>
+    <t>3117-650X</t>
+  </si>
+  <si>
+    <t>2773-126X</t>
+  </si>
+  <si>
+    <t>3050-9998</t>
+  </si>
+  <si>
+    <t>3051-2913</t>
+  </si>
+  <si>
+    <t>3051-3111</t>
+  </si>
+  <si>
+    <t>3117-325X</t>
+  </si>
+  <si>
+    <t>3117-5929</t>
+  </si>
+  <si>
+    <t>3117-3268</t>
+  </si>
+  <si>
+    <t>3117-6496</t>
+  </si>
+  <si>
+    <t>3117-5112</t>
+  </si>
+  <si>
+    <t>2949-9119</t>
+  </si>
+  <si>
+    <t>3051-231X</t>
+  </si>
+  <si>
+    <t>3051-2689</t>
+  </si>
+  <si>
+    <t>3051-3146</t>
+  </si>
+  <si>
+    <t>3051-2484</t>
+  </si>
+  <si>
+    <t>3051-1720</t>
+  </si>
+  <si>
+    <t>3117-3594</t>
+  </si>
+  <si>
+    <t>3117-4620</t>
+  </si>
+  <si>
+    <t>3117-3128</t>
+  </si>
+  <si>
+    <t>2772-9478</t>
+  </si>
+  <si>
+    <t>3051-4452</t>
+  </si>
+  <si>
+    <t>3117-4701</t>
+  </si>
+  <si>
+    <t>3050-7189</t>
+  </si>
+  <si>
+    <t>3051-3227</t>
+  </si>
+  <si>
+    <t>0021-7557</t>
+  </si>
+  <si>
+    <t>3051-2301</t>
+  </si>
+  <si>
+    <t>3051-1313</t>
+  </si>
+  <si>
+    <t>3051-1186</t>
+  </si>
+  <si>
+    <t>3117-3586</t>
+  </si>
+  <si>
+    <t>3051-0597</t>
+  </si>
+  <si>
+    <t>3051-0600</t>
+  </si>
+  <si>
+    <t>2603-6479</t>
+  </si>
+  <si>
+    <t>2667-100X</t>
+  </si>
+  <si>
+    <t>2468-0133</t>
+  </si>
+  <si>
+    <t>3051-0678</t>
+  </si>
+  <si>
+    <t>2471-5492</t>
+  </si>
+  <si>
+    <t>3117-3918</t>
+  </si>
+  <si>
+    <t>3117-471X</t>
+  </si>
+  <si>
+    <t>0003-5521</t>
+  </si>
+  <si>
+    <t>3117-5775</t>
+  </si>
+  <si>
+    <t>3117-387X</t>
+  </si>
+  <si>
+    <t>1386-1964</t>
+  </si>
+  <si>
+    <t>3117-5740</t>
+  </si>
+  <si>
+    <t>3051-1569</t>
+  </si>
+  <si>
+    <t>3051-2808</t>
+  </si>
+  <si>
+    <t>3117-468X</t>
+  </si>
+  <si>
+    <t>3117-3683</t>
+  </si>
+  <si>
+    <t>3117-5821</t>
+  </si>
+  <si>
+    <t>3117-678X</t>
+  </si>
+  <si>
+    <t>3051-3081</t>
+  </si>
+  <si>
+    <t>0079-6786</t>
+  </si>
+  <si>
+    <t>3051-276X</t>
+  </si>
+  <si>
+    <t>0034-8376</t>
+  </si>
+  <si>
+    <t>3051-0643</t>
+  </si>
+  <si>
+    <t>3051-052X</t>
+  </si>
+  <si>
+    <t>3117-5767</t>
+  </si>
+  <si>
+    <t>3051-2921</t>
+  </si>
+  <si>
+    <t>3050-5011</t>
+  </si>
+  <si>
+    <t>3117-4132</t>
+  </si>
+  <si>
+    <t>3117-5252</t>
+  </si>
+  <si>
+    <t>3117-4639</t>
+  </si>
+  <si>
+    <t>3117-5511</t>
+  </si>
+  <si>
+    <t>3051-360X</t>
+  </si>
+  <si>
+    <t>3117-3470</t>
+  </si>
+  <si>
+    <t>3117-3136</t>
+  </si>
+  <si>
+    <t>3117-3500</t>
+  </si>
+  <si>
+    <t>Elsevier</t>
+  </si>
+  <si>
+    <t>1590-8658</t>
+  </si>
+  <si>
+    <t>2212-4209</t>
+  </si>
+  <si>
+    <t>0889-1575</t>
+  </si>
+  <si>
+    <t>2352-4928</t>
+  </si>
+  <si>
+    <t>0981-9428</t>
+  </si>
+  <si>
+    <t>1550-7424</t>
+  </si>
+  <si>
+    <t>2451-9049</t>
+  </si>
+  <si>
+    <t>1467-2987</t>
+  </si>
+  <si>
+    <t>Digestive and Liver Disease</t>
+  </si>
+  <si>
+    <t>International Journal of Disaster Risk Reduction</t>
+  </si>
+  <si>
+    <t>Journal of Food Composition and Analysis</t>
+  </si>
+  <si>
+    <t>Materials Today Communications</t>
+  </si>
+  <si>
+    <t>Plant Physiology and Biochemistry</t>
+  </si>
+  <si>
+    <t>Rangeland Ecology &amp; Management</t>
+  </si>
+  <si>
+    <t>Thermal Science and Engineering Progress</t>
+  </si>
+  <si>
+    <t>Veterinary Anaesthesia and Analgesia</t>
+  </si>
+  <si>
+    <t>Flippar till Open</t>
+  </si>
+  <si>
+    <t>Arthroscopy Techniques</t>
+  </si>
+  <si>
+    <t>Arthroscopy, Sports Medicine, and Rehabilitation</t>
+  </si>
+  <si>
+    <t>Communications in Transportation Research</t>
+  </si>
+  <si>
+    <t>EFB Bioeconomy Journal</t>
+  </si>
+  <si>
+    <t>Emerging Animal Species</t>
+  </si>
+  <si>
+    <t>e-Prime - Advances in Electrical Engineering, Electronics and Energy</t>
+  </si>
+  <si>
+    <t>International Journal of Surgery Case Reports</t>
+  </si>
+  <si>
+    <t>IPEM-Translation</t>
+  </si>
+  <si>
+    <t>Journal of Equine Rehabilitation</t>
+  </si>
+  <si>
+    <t>Journal of Manipulative and Physiological Therapeutics</t>
+  </si>
+  <si>
+    <t>Journal of Non-Crystalline Solids: X</t>
+  </si>
+  <si>
+    <t>Marine and Petroleum Geology</t>
+  </si>
+  <si>
+    <t>Microbes and Infection</t>
+  </si>
+  <si>
+    <t>Molecular Therapy: Methods &amp; Clinical Development</t>
+  </si>
+  <si>
+    <t>Research in Microbiology</t>
+  </si>
+  <si>
+    <t>Reviews in Physics</t>
+  </si>
+  <si>
+    <t>Santé mentale et Droit</t>
+  </si>
+  <si>
+    <t>Science Talks</t>
+  </si>
+  <si>
+    <t>Water Resources and Economics</t>
+  </si>
+  <si>
+    <t>2772-4247</t>
+  </si>
+  <si>
+    <t>2667-0410</t>
+  </si>
+  <si>
+    <t>2772-8137</t>
+  </si>
+  <si>
+    <t>2772-6711</t>
+  </si>
+  <si>
+    <t>2210-2612</t>
+  </si>
+  <si>
+    <t>2667-2588</t>
+  </si>
+  <si>
+    <t>2949-9054</t>
+  </si>
+  <si>
+    <t>0161-4754</t>
+  </si>
+  <si>
+    <t>2590-1591</t>
+  </si>
+  <si>
+    <t>0264-8172</t>
+  </si>
+  <si>
+    <t>1286-4579</t>
+  </si>
+  <si>
+    <t>2329-0501</t>
+  </si>
+  <si>
+    <t>0027-5107</t>
+  </si>
+  <si>
+    <t>0923-2508</t>
+  </si>
+  <si>
+    <t>2405-4283</t>
+  </si>
+  <si>
+    <t>2772-9710</t>
+  </si>
+  <si>
+    <t>2772-5693</t>
+  </si>
+  <si>
+    <t>2212-4284</t>
+  </si>
+  <si>
+    <t>Emerald Publishing</t>
+  </si>
+  <si>
+    <t>3049-7914</t>
+  </si>
+  <si>
+    <t>3049-7922</t>
+  </si>
+  <si>
+    <t>Journal of Hospitality and Tourism Horizons</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/jhth</t>
+  </si>
+  <si>
+    <t>3049-9569</t>
+  </si>
+  <si>
+    <t>4D Printing</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/4dp</t>
+  </si>
+  <si>
+    <t>2977-0246</t>
+  </si>
+  <si>
+    <t>International Perspectives on Health Equity</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/iphee</t>
+  </si>
+  <si>
+    <t>2977-0114</t>
+  </si>
+  <si>
+    <t>Journal of Responsible Production and Consumption</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/jrpc</t>
+  </si>
+  <si>
+    <t>3029-0422</t>
+  </si>
+  <si>
+    <t>3029-0414</t>
+  </si>
+  <si>
+    <t>Machine Learning and Data Science in Geotechnics</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/mlag</t>
+  </si>
+  <si>
+    <t>2976-9310</t>
+  </si>
+  <si>
+    <t>Quality Education for All</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/qea</t>
+  </si>
+  <si>
+    <t>2976-8993</t>
+  </si>
+  <si>
+    <t>Urbanization, Sustainability and Society</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/insight/publication/issn/2976-8993</t>
   </si>
 </sst>
 </file>
@@ -5216,6 +6201,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB1BD5BB-E7EC-42D1-AA9C-0F2CA513C3AA}" name="Table1" displayName="Table1" ref="A1:H158" totalsRowShown="0">
+  <autoFilter ref="A1:H158" xr:uid="{FB1BD5BB-E7EC-42D1-AA9C-0F2CA513C3AA}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{B1C69512-1A5D-45C0-96E7-EE5DD5174A7C}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{5808679C-E917-405A-8EFE-C32FEB3A50FC}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{EC430C3B-D823-4959-A7E9-D28E34944BE3}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{939AC2D3-4D92-4C4C-BB4C-3594A2FAE46A}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{ADA8A525-E987-479E-926E-4E50BB40BF21}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{D2BB4442-BD64-4D7D-A782-CAFA127D7B25}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{C200BD38-12D4-4EA4-A292-80FA41D2D3BF}" name="CC License options"/>
+    <tableColumn id="8" xr3:uid="{A9C8E2CC-55E5-46C9-8471-6F11F6FDED2C}" name="Ändring"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17570,4 +18572,3298 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{235F959E-7839-41C5-9B5C-EA98F4D4E2ED}">
+  <dimension ref="A1:H158"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="47.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>593</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1719</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>593</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>593</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>593</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>589</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>593</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>589</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>593</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>593</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>589</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>593</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1735</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1736</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>593</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>589</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>593</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>589</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>593</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>589</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>593</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>589</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>593</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>589</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>593</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>589</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>593</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>589</v>
+      </c>
+      <c r="B19" t="s">
+        <v>861</v>
+      </c>
+      <c r="D19" t="s">
+        <v>863</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1754</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>593</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>589</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1755</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>593</v>
+      </c>
+      <c r="H20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>589</v>
+      </c>
+      <c r="B21" t="s">
+        <v>627</v>
+      </c>
+      <c r="D21" t="s">
+        <v>628</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>593</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>589</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1757</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>593</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>589</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>593</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>589</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>593</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>589</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1767</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>593</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>589</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>611</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>589</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>593</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>589</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1776</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>593</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D29" t="s">
+        <v>637</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B34" t="s">
+        <v>655</v>
+      </c>
+      <c r="D34" t="s">
+        <v>656</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1782</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1785</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1790</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1794</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1795</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B55" t="s">
+        <v>723</v>
+      </c>
+      <c r="D55" t="s">
+        <v>725</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1807</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1808</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1812</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1814</v>
+      </c>
+      <c r="F68" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1817</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F83" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1831</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1834</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>13</v>
+      </c>
+      <c r="H89" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1837</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1838</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F94" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1846</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>13</v>
+      </c>
+      <c r="H100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1849</v>
+      </c>
+      <c r="F103" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" t="s">
+        <v>13</v>
+      </c>
+      <c r="H103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>13</v>
+      </c>
+      <c r="H104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F105" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>13</v>
+      </c>
+      <c r="H105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F106" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" t="s">
+        <v>13</v>
+      </c>
+      <c r="H106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F108" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>13</v>
+      </c>
+      <c r="H108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1855</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" t="s">
+        <v>13</v>
+      </c>
+      <c r="H109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1858</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" t="s">
+        <v>13</v>
+      </c>
+      <c r="H112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F113" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F114" t="s">
+        <v>18</v>
+      </c>
+      <c r="G114" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1862</v>
+      </c>
+      <c r="F116" t="s">
+        <v>18</v>
+      </c>
+      <c r="G116" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F117" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F118" t="s">
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F119" t="s">
+        <v>18</v>
+      </c>
+      <c r="G119" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F120" t="s">
+        <v>18</v>
+      </c>
+      <c r="G120" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F121" t="s">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F122" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>13</v>
+      </c>
+      <c r="H122" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F123" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>13</v>
+      </c>
+      <c r="H123" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F124" t="s">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F125" t="s">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>13</v>
+      </c>
+      <c r="H125" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F126" t="s">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F127" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>13</v>
+      </c>
+      <c r="H127" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F128" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F129" t="s">
+        <v>18</v>
+      </c>
+      <c r="G129" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F130" t="s">
+        <v>12</v>
+      </c>
+      <c r="G130" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F131" t="s">
+        <v>18</v>
+      </c>
+      <c r="G131" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F132" t="s">
+        <v>18</v>
+      </c>
+      <c r="G132" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1978</v>
+      </c>
+      <c r="F133" t="s">
+        <v>18</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F134" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F135" t="s">
+        <v>18</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1981</v>
+      </c>
+      <c r="F136" t="s">
+        <v>18</v>
+      </c>
+      <c r="G136" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1982</v>
+      </c>
+      <c r="F137" t="s">
+        <v>18</v>
+      </c>
+      <c r="G137" t="s">
+        <v>13</v>
+      </c>
+      <c r="H137" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B138" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F138" t="s">
+        <v>18</v>
+      </c>
+      <c r="G138" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B139" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F139" t="s">
+        <v>18</v>
+      </c>
+      <c r="G139" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B140" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F140" t="s">
+        <v>12</v>
+      </c>
+      <c r="G140" t="s">
+        <v>13</v>
+      </c>
+      <c r="H140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B141" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1986</v>
+      </c>
+      <c r="F141" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" t="s">
+        <v>13</v>
+      </c>
+      <c r="H141" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B142" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D142" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F142" t="s">
+        <v>12</v>
+      </c>
+      <c r="G142" t="s">
+        <v>13</v>
+      </c>
+      <c r="H142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B143" t="s">
+        <v>544</v>
+      </c>
+      <c r="D143" t="s">
+        <v>546</v>
+      </c>
+      <c r="F143" t="s">
+        <v>12</v>
+      </c>
+      <c r="G143" t="s">
+        <v>13</v>
+      </c>
+      <c r="H143" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B144" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D144" t="s">
+        <v>1988</v>
+      </c>
+      <c r="F144" t="s">
+        <v>12</v>
+      </c>
+      <c r="G144" t="s">
+        <v>13</v>
+      </c>
+      <c r="H144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B145" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F145" t="s">
+        <v>18</v>
+      </c>
+      <c r="G145" t="s">
+        <v>13</v>
+      </c>
+      <c r="H145" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B146" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F146" t="s">
+        <v>12</v>
+      </c>
+      <c r="G146" t="s">
+        <v>13</v>
+      </c>
+      <c r="H146" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B147" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F147" t="s">
+        <v>12</v>
+      </c>
+      <c r="G147" t="s">
+        <v>13</v>
+      </c>
+      <c r="H147" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B148" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1991</v>
+      </c>
+      <c r="F148" t="s">
+        <v>18</v>
+      </c>
+      <c r="G148" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B149" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F149" t="s">
+        <v>12</v>
+      </c>
+      <c r="G149" t="s">
+        <v>13</v>
+      </c>
+      <c r="H149" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B150" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1993</v>
+      </c>
+      <c r="F150" t="s">
+        <v>18</v>
+      </c>
+      <c r="G150" t="s">
+        <v>13</v>
+      </c>
+      <c r="H150" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B151" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F151" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151" t="s">
+        <v>13</v>
+      </c>
+      <c r="H151" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B152" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C152" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E152" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F152" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" t="s">
+        <v>13</v>
+      </c>
+      <c r="H152" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B153" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D153" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E153" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F153" t="s">
+        <v>12</v>
+      </c>
+      <c r="G153" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B154" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D154" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E154" t="s">
+        <v>2023</v>
+      </c>
+      <c r="F154" t="s">
+        <v>18</v>
+      </c>
+      <c r="G154" t="s">
+        <v>13</v>
+      </c>
+      <c r="H154" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B155" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D155" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E155" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F155" t="s">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>13</v>
+      </c>
+      <c r="H155" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B156" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C156" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D156" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E156" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F156" t="s">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>13</v>
+      </c>
+      <c r="H156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B157" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D157" t="s">
+        <v>2032</v>
+      </c>
+      <c r="E157" t="s">
+        <v>2033</v>
+      </c>
+      <c r="F157" t="s">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>13</v>
+      </c>
+      <c r="H157" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B158" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D158" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E158" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F158" t="s">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>13</v>
+      </c>
+      <c r="H158" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8169E96-4C60-462E-ADAE-88E463E82EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C918367E-F41F-46A6-8170-952D8E10458A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
     <sheet name="Nr2_Jan19" sheetId="2" r:id="rId2"/>
     <sheet name="Rättningar_Jan20" sheetId="3" r:id="rId3"/>
     <sheet name="Nr3_Feb16" sheetId="4" r:id="rId4"/>
+    <sheet name="Nr4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4673" uniqueCount="2037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4861" uniqueCount="2127">
   <si>
     <t>Imprint</t>
   </si>
@@ -6139,6 +6140,276 @@
   </si>
   <si>
     <t>https://www.emerald.com/insight/publication/issn/2976-8993</t>
+  </si>
+  <si>
+    <t>Royal Society of Medicine</t>
+  </si>
+  <si>
+    <t>2053-3705</t>
+  </si>
+  <si>
+    <t>2053-3691</t>
+  </si>
+  <si>
+    <t>Post Reproductive Health</t>
+  </si>
+  <si>
+    <t>http://journals.sagepub.com/home/min</t>
+  </si>
+  <si>
+    <t>2048-0040</t>
+  </si>
+  <si>
+    <t>JRSM Cardiovascular Disease</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/CVD</t>
+  </si>
+  <si>
+    <t>3091-292X</t>
+  </si>
+  <si>
+    <t>Communications AI &amp; Computing</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/commsaicomp/</t>
+  </si>
+  <si>
+    <t>IOS Press</t>
+  </si>
+  <si>
+    <t>2352-3735</t>
+  </si>
+  <si>
+    <t>2352-3727</t>
+  </si>
+  <si>
+    <t>Bladder Cancer</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/BLC</t>
+  </si>
+  <si>
+    <t>1558-1551</t>
+  </si>
+  <si>
+    <t>0888-6008</t>
+  </si>
+  <si>
+    <t>Breast Disease</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/BRD</t>
+  </si>
+  <si>
+    <t>1875-8592</t>
+  </si>
+  <si>
+    <t>1574-0153</t>
+  </si>
+  <si>
+    <t>Cancer Biomarkers</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/CBM</t>
+  </si>
+  <si>
+    <t>2451-8492</t>
+  </si>
+  <si>
+    <t>2451-8484</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/dsca</t>
+  </si>
+  <si>
+    <t>2949-799X</t>
+  </si>
+  <si>
+    <t>FAIR Connect</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/fco</t>
+  </si>
+  <si>
+    <t>1875-8681</t>
+  </si>
+  <si>
+    <t>0169-2968</t>
+  </si>
+  <si>
+    <t>Fundamenta Informaticae</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/FUN</t>
+  </si>
+  <si>
+    <t>1434-3207</t>
+  </si>
+  <si>
+    <t>1386-6338</t>
+  </si>
+  <si>
+    <t>In Silico Biology</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/isia</t>
+  </si>
+  <si>
+    <t>2589-9961</t>
+  </si>
+  <si>
+    <t>2589-9953</t>
+  </si>
+  <si>
+    <t>Journal of Future Robot Life</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/frl</t>
+  </si>
+  <si>
+    <t>1875-8789</t>
+  </si>
+  <si>
+    <t>0167-5265</t>
+  </si>
+  <si>
+    <t>Information Services and Use</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/ISU</t>
+  </si>
+  <si>
+    <t>1878-5395</t>
+  </si>
+  <si>
+    <t>0378-777X</t>
+  </si>
+  <si>
+    <t>Environmental Policy and Law</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/EPL</t>
+  </si>
+  <si>
+    <t>2214-3602</t>
+  </si>
+  <si>
+    <t>2214-3599</t>
+  </si>
+  <si>
+    <t>Journal of Neuromuscular Diseases</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/jnd</t>
+  </si>
+  <si>
+    <t>1877-718X</t>
+  </si>
+  <si>
+    <t>1877-7171</t>
+  </si>
+  <si>
+    <t>Journal of Parkinson's Disease</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/pkn</t>
+  </si>
+  <si>
+    <t>1875-8894</t>
+  </si>
+  <si>
+    <t>1874-5393</t>
+  </si>
+  <si>
+    <t>Journal of Pediatric Rehabilitation Medicine</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/prm</t>
+  </si>
+  <si>
+    <t>2215-0218</t>
+  </si>
+  <si>
+    <t>2215-020X</t>
+  </si>
+  <si>
+    <t>Journal of Sports Analytics</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/san</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2468-4570 </t>
+  </si>
+  <si>
+    <t>2468-4562</t>
+  </si>
+  <si>
+    <t>Kidney Cancer</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/kca</t>
+  </si>
+  <si>
+    <t>2949-8732</t>
+  </si>
+  <si>
+    <t>Neurosymbolic Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>https://neurosymbolic-ai-journal.com/content/about-neurosymbolic-artificial-intelligence</t>
+  </si>
+  <si>
+    <t>2451-9502</t>
+  </si>
+  <si>
+    <t>2451-9480</t>
+  </si>
+  <si>
+    <t>Nutrition and Healty Aging</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/nut</t>
+  </si>
+  <si>
+    <t>2210-4968</t>
+  </si>
+  <si>
+    <t>1570-0844</t>
+  </si>
+  <si>
+    <t>Semantic Web</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/swj</t>
+  </si>
+  <si>
+    <t>2468-8304</t>
+  </si>
+  <si>
+    <t>2468-8290</t>
+  </si>
+  <si>
+    <t>Stem Journal</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/ste</t>
+  </si>
+  <si>
+    <t>1010-4283</t>
+  </si>
+  <si>
+    <t>1423-0380</t>
+  </si>
+  <si>
+    <t>Tumor Biology</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/tub</t>
   </si>
 </sst>
 </file>
@@ -21866,4 +22137,630 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66CF5B3A-DA21-4E56-8131-404A7224AF69}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2056</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2066</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2067</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2075</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2079</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2107</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2125</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2126</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C918367E-F41F-46A6-8170-952D8E10458A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE01A57F-DA94-43A2-86F5-B139127591F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
     <sheet name="Nr2_Jan19" sheetId="2" r:id="rId2"/>
     <sheet name="Rättningar_Jan20" sheetId="3" r:id="rId3"/>
     <sheet name="Nr3_Feb16" sheetId="4" r:id="rId4"/>
-    <sheet name="Nr4" sheetId="5" r:id="rId5"/>
+    <sheet name="Nr4_Mars6" sheetId="5" r:id="rId5"/>
+    <sheet name="Nr5_Mars16" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4861" uniqueCount="2127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5298" uniqueCount="2281">
   <si>
     <t>Imprint</t>
   </si>
@@ -6410,6 +6411,468 @@
   </si>
   <si>
     <t>https://journals.sagepub.com/home/tub</t>
+  </si>
+  <si>
+    <t>Sage</t>
+  </si>
+  <si>
+    <t>2330-5517</t>
+  </si>
+  <si>
+    <t>2472-3444</t>
+  </si>
+  <si>
+    <t>AATCC Journal of Research</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/aata</t>
+  </si>
+  <si>
+    <t>byter publiceringsmodell till Open</t>
+  </si>
+  <si>
+    <t>2167-9010</t>
+  </si>
+  <si>
+    <t>0360-1293</t>
+  </si>
+  <si>
+    <t>Acupuncture &amp; Electro-Therapeutics Research</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/AET</t>
+  </si>
+  <si>
+    <t>1544-0737</t>
+  </si>
+  <si>
+    <t>0895-9374</t>
+  </si>
+  <si>
+    <t>Advances in Dental Research</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/ADR</t>
+  </si>
+  <si>
+    <t>1913-701X</t>
+  </si>
+  <si>
+    <t>1715-1635</t>
+  </si>
+  <si>
+    <t>Canadian Pharmacists Journal</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/CPH</t>
+  </si>
+  <si>
+    <t>2977-649X</t>
+  </si>
+  <si>
+    <t>2977-6481</t>
+  </si>
+  <si>
+    <t>Design for Augmented Humanity</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/DAH</t>
+  </si>
+  <si>
+    <t>3049-7671</t>
+  </si>
+  <si>
+    <t>Designing</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/DES</t>
+  </si>
+  <si>
+    <t>8755-2930</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/eqs</t>
+  </si>
+  <si>
+    <t>3068-1391</t>
+  </si>
+  <si>
+    <t>2154-1647</t>
+  </si>
+  <si>
+    <t>Education and Training in Autism and Developmental Disabilities</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/ETA</t>
+  </si>
+  <si>
+    <t>2396-9873</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/ESO</t>
+  </si>
+  <si>
+    <t>1746-6067</t>
+  </si>
+  <si>
+    <t>0306-4220</t>
+  </si>
+  <si>
+    <t>Index on Censorship</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/IOC</t>
+  </si>
+  <si>
+    <t>1755-7399</t>
+  </si>
+  <si>
+    <t>1755-7380</t>
+  </si>
+  <si>
+    <t>InnovAiT</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/INO</t>
+  </si>
+  <si>
+    <t>1930-076X</t>
+  </si>
+  <si>
+    <t>1558-6235</t>
+  </si>
+  <si>
+    <t>International Journal of Sport Finance</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/SFJ</t>
+  </si>
+  <si>
+    <t>2321-0311</t>
+  </si>
+  <si>
+    <t>2278-6821</t>
+  </si>
+  <si>
+    <t>Jindal Journal of Business Research</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/BRJ</t>
+  </si>
+  <si>
+    <t>Borttagen (ersatt av Jindal Management Journal)</t>
+  </si>
+  <si>
+    <t>3049-7884</t>
+  </si>
+  <si>
+    <t>3049-7876</t>
+  </si>
+  <si>
+    <t>Jindal Management Journal</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/BRJ</t>
+  </si>
+  <si>
+    <t>1460-3578</t>
+  </si>
+  <si>
+    <t>0022-3433</t>
+  </si>
+  <si>
+    <t>Journal of Peace Research</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/JPR</t>
+  </si>
+  <si>
+    <t>2397-1991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2397-1983 </t>
+  </si>
+  <si>
+    <t>Journal of Scleroderma and Related Disorders</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/JSO</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/PAJ</t>
+  </si>
+  <si>
+    <t>2765-7272</t>
+  </si>
+  <si>
+    <t>2765-2157</t>
+  </si>
+  <si>
+    <t>Journal of Smart Tourism</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/SMT</t>
+  </si>
+  <si>
+    <t>2042-8189</t>
+  </si>
+  <si>
+    <t>1478-2715</t>
+  </si>
+  <si>
+    <t>Journal of the Royal College of Physicians of Edinburgh</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/RCP</t>
+  </si>
+  <si>
+    <t>2976-9450</t>
+  </si>
+  <si>
+    <t>2976-9442</t>
+  </si>
+  <si>
+    <t>Journal of World Affairs</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/WAJ</t>
+  </si>
+  <si>
+    <t>2977-7992</t>
+  </si>
+  <si>
+    <t>2977-7984</t>
+  </si>
+  <si>
+    <t>Media, Technology and Governance</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/MAG</t>
+  </si>
+  <si>
+    <t>2376-4791</t>
+  </si>
+  <si>
+    <t>0739-5329</t>
+  </si>
+  <si>
+    <t>Newspaper Research Journal</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/NRJ</t>
+  </si>
+  <si>
+    <t>Borttagen (ersatt av News Research Journal)</t>
+  </si>
+  <si>
+    <t>3049-785X</t>
+  </si>
+  <si>
+    <t>3049-7841</t>
+  </si>
+  <si>
+    <t>News Research Journal</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/NRJ</t>
+  </si>
+  <si>
+    <t>1940-6487</t>
+  </si>
+  <si>
+    <t>0031-7217</t>
+  </si>
+  <si>
+    <t>Phi Delta Kappan</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/PDK</t>
+  </si>
+  <si>
+    <t>2041-9066</t>
+  </si>
+  <si>
+    <t>2041-9058</t>
+  </si>
+  <si>
+    <t>Political Insight</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/PLI</t>
+  </si>
+  <si>
+    <t>2978-431X</t>
+  </si>
+  <si>
+    <t>0970-8448</t>
+  </si>
+  <si>
+    <t>Prajnan</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/PJN</t>
+  </si>
+  <si>
+    <t>0967-0106</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/SDI</t>
+  </si>
+  <si>
+    <t>3033-3717</t>
+  </si>
+  <si>
+    <t>Sex &amp; Sexualities</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/SNS</t>
+  </si>
+  <si>
+    <t>1557-2528</t>
+  </si>
+  <si>
+    <t>1061-6934</t>
+  </si>
+  <si>
+    <t>Sport Marketing Quarterly</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/QSM</t>
+  </si>
+  <si>
+    <t>1179-5441</t>
+  </si>
+  <si>
+    <t>Clinical Medicine Insights: Arthritis and Musculoskeletal Disorders</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/AMD</t>
+  </si>
+  <si>
+    <t>ändrar publiceringsmodell till hybrid</t>
+  </si>
+  <si>
+    <t>1179-5565</t>
+  </si>
+  <si>
+    <t>Clinical Medicine Insights: Pediatrics</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/PDI</t>
+  </si>
+  <si>
+    <t>1178-6469</t>
+  </si>
+  <si>
+    <t>International Journal of Tryptophan Research</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/TRY</t>
+  </si>
+  <si>
+    <t>1752-8976</t>
+  </si>
+  <si>
+    <t>1470-3203</t>
+  </si>
+  <si>
+    <t>Journal of the Renin-Angiotensin-Aldosterone System</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/JRA</t>
+  </si>
+  <si>
+    <t>1940-0829</t>
+  </si>
+  <si>
+    <t>Tropical Conservation Science</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/TRC</t>
+  </si>
+  <si>
+    <t>2329-048X</t>
+  </si>
+  <si>
+    <t>Child Neurology Open</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/CNO</t>
+  </si>
+  <si>
+    <t>2632-010X</t>
+  </si>
+  <si>
+    <t>Clinical Pathology</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/PAT</t>
+  </si>
+  <si>
+    <t>Byter namn till SAGE Open Pathology, samma ISSN</t>
+  </si>
+  <si>
+    <t>SAGE Open Pathology</t>
+  </si>
+  <si>
+    <t>Namnbyte från Clinical Pathology, samma ISSN</t>
+  </si>
+  <si>
+    <t>2333-7214</t>
+  </si>
+  <si>
+    <t>Gerontology and Geriatric Medicine</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/GGM</t>
+  </si>
+  <si>
+    <t>Byter namn till SAGE Open Aging, samma ISSN</t>
+  </si>
+  <si>
+    <t>SAGE Open Aging</t>
+  </si>
+  <si>
+    <t>Namnbyte från Gerontology and Geriatric Medicine, samma ISSN</t>
+  </si>
+  <si>
+    <t>2333-794X</t>
+  </si>
+  <si>
+    <t>Global Pediatric Health</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/GPH</t>
+  </si>
+  <si>
+    <t>Byter namn till SAGE Open Pediatrics, samma ISSN</t>
+  </si>
+  <si>
+    <t>SAGE Open Pediatrics</t>
+  </si>
+  <si>
+    <t>Namnbyte från Global Pediatric Health, samma ISSN</t>
+  </si>
+  <si>
+    <t>2542-4823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Alzheimer's Disease Reports </t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/ALR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of the Royal Society of Medicine Cardiovascular Disease </t>
+  </si>
+  <si>
+    <t>http://journals.sagepub.com/home/cvd</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/SEA</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/nax</t>
   </si>
 </sst>
 </file>
@@ -6433,7 +6896,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -6450,13 +6913,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22763,4 +23242,1442 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{361601DD-BF9C-42E1-A975-C440534ED8E0}">
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="43.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2140</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2143</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2144</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2148</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2166</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2167</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2171</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2175</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2180</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2184</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2189</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2193</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2201</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2205</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2218</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2226</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2242</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2245</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2249</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2056</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2255</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E42" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2264</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2264</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2270</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2270</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2075</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2278</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2103</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2279</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2117</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2125</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2126</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE01A57F-DA94-43A2-86F5-B139127591F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8390B5B8-6AD7-4A7A-B970-F760DFC5B974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Nr3_Feb16" sheetId="4" r:id="rId4"/>
     <sheet name="Nr4_Mars6" sheetId="5" r:id="rId5"/>
     <sheet name="Nr5_Mars16" sheetId="6" r:id="rId6"/>
+    <sheet name="Nr6_April13" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5298" uniqueCount="2281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5464" uniqueCount="2354">
   <si>
     <t>Imprint</t>
   </si>
@@ -6873,6 +6874,225 @@
   </si>
   <si>
     <t>https://journals.sagepub.com/home/nax</t>
+  </si>
+  <si>
+    <t>1460-2245</t>
+  </si>
+  <si>
+    <t>Health Promotion International</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/heapro</t>
+  </si>
+  <si>
+    <t>Flippar till open</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/jpr</t>
+  </si>
+  <si>
+    <t>2475-7241</t>
+  </si>
+  <si>
+    <t>The Journal of Applied Laboratory Medicine</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/jalm</t>
+  </si>
+  <si>
+    <t>1399-5448</t>
+  </si>
+  <si>
+    <t>Pediatric Diabetes</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/pedi</t>
+  </si>
+  <si>
+    <t>Borttagen (bytt förlag från Wiley till Maximum Academic Press)</t>
+  </si>
+  <si>
+    <t>2978-8250</t>
+  </si>
+  <si>
+    <t>Transplant and Transfusion</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/trtr</t>
+  </si>
+  <si>
+    <t>2978-8269</t>
+  </si>
+  <si>
+    <t>Women's Health in Primary Care</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/whpc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2978-8277  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Perioperative Care </t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/jpoc</t>
+  </si>
+  <si>
+    <t>2978-8242</t>
+  </si>
+  <si>
+    <t>Simulation in Healthcare Education</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/sihe</t>
+  </si>
+  <si>
+    <t>1759-7390</t>
+  </si>
+  <si>
+    <t>British Journal of Hospital Medicine</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/hmed</t>
+  </si>
+  <si>
+    <t>Bristol University Press</t>
+  </si>
+  <si>
+    <t>2755-6654</t>
+  </si>
+  <si>
+    <t>Feminism and Organization</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypress.co.uk/journals/feminism-and-organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3033-3660 </t>
+  </si>
+  <si>
+    <t>Gender and Justice</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypressdigital.com/view/journals/gj/gj-overview.xml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3050-2969 </t>
+  </si>
+  <si>
+    <t>Journal of Creative Research Methods</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypressdigital.com/view/journals/jcrm/jcrm-overview.xml</t>
+  </si>
+  <si>
+    <t>3049-8414</t>
+  </si>
+  <si>
+    <t>Journal of Disappearance Studies</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypressdigital.com/view/journals/jds/jds-overview.xml</t>
+  </si>
+  <si>
+    <t>2978-2066</t>
+  </si>
+  <si>
+    <t>Pluriversal International Relations</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypress.co.uk/journals/pluriversal-international-relations</t>
+  </si>
+  <si>
+    <t>PLOS</t>
+  </si>
+  <si>
+    <t>3070-801X</t>
+  </si>
+  <si>
+    <t>PLOS Aging and Health</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/agingandhealth/</t>
+  </si>
+  <si>
+    <t>3070-8141</t>
+  </si>
+  <si>
+    <t>PLOS Ecosystems</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/ecosystems/</t>
+  </si>
+  <si>
+    <t>Hindawi (Wiley)</t>
+  </si>
+  <si>
+    <t>3069-8359</t>
+  </si>
+  <si>
+    <t>Thrombosis and Circulation Research</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/30698359</t>
+  </si>
+  <si>
+    <t>3035-9880</t>
+  </si>
+  <si>
+    <t> 0349-8808</t>
+  </si>
+  <si>
+    <t>Adoranten</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/adoranten</t>
+  </si>
+  <si>
+    <t>2004-3929</t>
+  </si>
+  <si>
+    <t>2000-9216</t>
+  </si>
+  <si>
+    <t>Högskolepedagogisk debatt</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/hpdebatt</t>
+  </si>
+  <si>
+    <t>1404-9430</t>
+  </si>
+  <si>
+    <t>0015-7813</t>
+  </si>
+  <si>
+    <t>Fornvännen: Journal of Swedish Antiquarian Research</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/fornvannen</t>
+  </si>
+  <si>
+    <t>2001-7286</t>
+  </si>
+  <si>
+    <t>1100-2573</t>
+  </si>
+  <si>
+    <t>lambda nordica</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/lambdanordica</t>
+  </si>
+  <si>
+    <t>2002-4665</t>
+  </si>
+  <si>
+    <t>European Journal of Philosophy in Arts Education</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/ejpae</t>
   </si>
 </sst>
 </file>
@@ -24680,4 +24900,561 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCBF5F0E-0A8D-438A-82AF-F3092B67097F}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>593</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>611</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2334</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>611</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2295</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2298</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2301</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2306</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2311</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2313</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2314</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2320</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2323</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2330</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>606</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2338</v>
+      </c>
+      <c r="F19" t="s">
+        <v>610</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>606</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2342</v>
+      </c>
+      <c r="F20" t="s">
+        <v>610</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>606</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2346</v>
+      </c>
+      <c r="F21" t="s">
+        <v>610</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>606</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2349</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2350</v>
+      </c>
+      <c r="F22" t="s">
+        <v>610</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>606</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F23" t="s">
+        <v>610</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8390B5B8-6AD7-4A7A-B970-F760DFC5B974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0450E6-DFDA-4318-A895-5A9EB0430ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Nr4_Mars6" sheetId="5" r:id="rId5"/>
     <sheet name="Nr5_Mars16" sheetId="6" r:id="rId6"/>
     <sheet name="Nr6_April13" sheetId="7" r:id="rId7"/>
+    <sheet name="Rättningar_April16" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5464" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5493" uniqueCount="2355">
   <si>
     <t>Imprint</t>
   </si>
@@ -7093,6 +7094,9 @@
   </si>
   <si>
     <t>https://publicera.kb.se/ejpae</t>
+  </si>
+  <si>
+    <t>Tar bort, blev felaktigt tillagd i uppdatering 6</t>
   </si>
 </sst>
 </file>
@@ -25457,4 +25461,109 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C4AC14-6653-464E-95B3-5FC270042EE8}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2311</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0450E6-DFDA-4318-A895-5A9EB0430ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630CDB33-6C8D-4196-A705-AFE96BB34C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Nr5_Mars16" sheetId="6" r:id="rId6"/>
     <sheet name="Nr6_April13" sheetId="7" r:id="rId7"/>
     <sheet name="Rättningar_April16" sheetId="8" r:id="rId8"/>
+    <sheet name="Nr7_Juni1" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5493" uniqueCount="2355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5853" uniqueCount="2491">
   <si>
     <t>Imprint</t>
   </si>
@@ -7097,6 +7098,414 @@
   </si>
   <si>
     <t>Tar bort, blev felaktigt tillagd i uppdatering 6</t>
+  </si>
+  <si>
+    <t>2376-7626</t>
+  </si>
+  <si>
+    <t>1195-6860</t>
+  </si>
+  <si>
+    <t>Ecoscience</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TECO</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TMPT</t>
+  </si>
+  <si>
+    <t>3068-4781</t>
+  </si>
+  <si>
+    <t>Global South Literary Studies</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/RGSL</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TIJE</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TIJR</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TITR</t>
+  </si>
+  <si>
+    <t>2471-2620</t>
+  </si>
+  <si>
+    <t>1071-4839</t>
+  </si>
+  <si>
+    <t>Nacla Report On The Americas</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/RNAC</t>
+  </si>
+  <si>
+    <t>1715-3379</t>
+  </si>
+  <si>
+    <t>0030-851X</t>
+  </si>
+  <si>
+    <t>Pacific Affairs</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/RPAF</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TPRH</t>
+  </si>
+  <si>
+    <t>3069-972X</t>
+  </si>
+  <si>
+    <t>Research in Food Engineering and Technology</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TFEN</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/KTRN</t>
+  </si>
+  <si>
+    <t>3068-1618</t>
+  </si>
+  <si>
+    <t>Asa Discoveries</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/UASD</t>
+  </si>
+  <si>
+    <t>3070-0485</t>
+  </si>
+  <si>
+    <t>Journal Of Research On Research</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/RROR</t>
+  </si>
+  <si>
+    <t>2045-0893</t>
+  </si>
+  <si>
+    <t>2045-0885</t>
+  </si>
+  <si>
+    <t>Melanoma Management</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/IMMT</t>
+  </si>
+  <si>
+    <t>1179-1543</t>
+  </si>
+  <si>
+    <t>Open Access Journal of Sports Medicine</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/DJSM</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/TOMR</t>
+  </si>
+  <si>
+    <t>1179-271X</t>
+  </si>
+  <si>
+    <t>Patient Related Outcome Measures</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/DPRO</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/IOCC</t>
+  </si>
+  <si>
+    <t>1365-2192</t>
+  </si>
+  <si>
+    <t>Chemistry International</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/ci/html</t>
+  </si>
+  <si>
+    <t>Ny titel</t>
+  </si>
+  <si>
+    <t>1838-0212</t>
+  </si>
+  <si>
+    <t>The Clinical Biochemist Reviews</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/aacbcbr/html</t>
+  </si>
+  <si>
+    <t>De Gruyter GmbH</t>
+  </si>
+  <si>
+    <t>2197-912X</t>
+  </si>
+  <si>
+    <t>0044-2674</t>
+  </si>
+  <si>
+    <t>Zeitschrift für Evangelische Ethik</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/zee/html</t>
+  </si>
+  <si>
+    <t>2198-0454</t>
+  </si>
+  <si>
+    <t>0342-2410</t>
+  </si>
+  <si>
+    <t>Verkündigung und Forschung</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/vf/html</t>
+  </si>
+  <si>
+    <t>2198-0462</t>
+  </si>
+  <si>
+    <t>0946-3518</t>
+  </si>
+  <si>
+    <t>Praktische Theologie</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/prth/html</t>
+  </si>
+  <si>
+    <t>2198-0470</t>
+  </si>
+  <si>
+    <t>0014-3502</t>
+  </si>
+  <si>
+    <t>Evangelische Theologie</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/evth/html</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/ijli/html</t>
+  </si>
+  <si>
+    <t>2543-683X</t>
+  </si>
+  <si>
+    <t>Journal of Data and Information Science</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/jdis/html</t>
+  </si>
+  <si>
+    <t>2944-5698</t>
+  </si>
+  <si>
+    <t>World Vocational and Technical Education</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/wvte/html</t>
+  </si>
+  <si>
+    <t>3052-8771</t>
+  </si>
+  <si>
+    <t>Open Transport</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/ot/o/html</t>
+  </si>
+  <si>
+    <t>3052-878X</t>
+  </si>
+  <si>
+    <t>3052-8798</t>
+  </si>
+  <si>
+    <t>Transport Phenomena</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/tp/html</t>
+  </si>
+  <si>
+    <t>3053-1683</t>
+  </si>
+  <si>
+    <t>3053-1675</t>
+  </si>
+  <si>
+    <t>Journal for the Preservation of Library and Archival Material</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/rest/html</t>
+  </si>
+  <si>
+    <t>1097-3702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugoye: Journal of Syriac Studies </t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/hug</t>
+  </si>
+  <si>
+    <t>Borttagen titel, partnertitel som inte ingår i avtalet</t>
+  </si>
+  <si>
+    <t>1863-5490</t>
+  </si>
+  <si>
+    <t>Medizinische Genetik</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/medgen</t>
+  </si>
+  <si>
+    <t>Borttagen titel, endast läsning</t>
+  </si>
+  <si>
+    <t>1865-8431</t>
+  </si>
+  <si>
+    <t>Restaurator. International Journal for the Preservation of Library and Archival Material</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/rest</t>
+  </si>
+  <si>
+    <t>Borttagen titel</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/nanoph</t>
+  </si>
+  <si>
+    <t>2195-4720</t>
+  </si>
+  <si>
+    <t>Pteridines</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/pteridines</t>
+  </si>
+  <si>
+    <t>2197-6376</t>
+  </si>
+  <si>
+    <t>Public History Weekly</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/phw</t>
+  </si>
+  <si>
+    <t>2198-0330</t>
+  </si>
+  <si>
+    <t>Zeitschrift für interkulturelle Germanistik</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/zrs</t>
+  </si>
+  <si>
+    <t>2219-4029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Language Relationship </t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/jlr</t>
+  </si>
+  <si>
+    <t>2296-4126</t>
+  </si>
+  <si>
+    <t>Zeitschrift für Medienwissenschaft</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/zfmw</t>
+  </si>
+  <si>
+    <t>2544-9826</t>
+  </si>
+  <si>
+    <t>Open Health</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/ohe</t>
+  </si>
+  <si>
+    <t>2688-4747</t>
+  </si>
+  <si>
+    <t>Journal of the Canadian Society for Syriac Studies</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/jcsss</t>
+  </si>
+  <si>
+    <t>2747-5093</t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/dak</t>
+  </si>
+  <si>
+    <t>2941-0002</t>
+  </si>
+  <si>
+    <t>Zeitschrift für archäologische Aufklärung</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/zfaa</t>
+  </si>
+  <si>
+    <t>De Gruyter Mouton</t>
+  </si>
+  <si>
+    <t>2192-9513</t>
+  </si>
+  <si>
+    <t>2192-9505</t>
+  </si>
+  <si>
+    <t>Chinese Journal of Applied Linguistics</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/cjal</t>
+  </si>
+  <si>
+    <t>Ändrad publiceringsmodell, tidigare felaktig</t>
+  </si>
+  <si>
+    <t>2235-5871</t>
+  </si>
+  <si>
+    <t>0004-4717</t>
+  </si>
+  <si>
+    <t>Asiatische Studien - Études Asiatiques</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/asia</t>
+  </si>
+  <si>
+    <t>Deutscher Kunstverlag (DKV)</t>
+  </si>
+  <si>
+    <t>0947-031X</t>
   </si>
 </sst>
 </file>
@@ -7120,7 +7529,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -7152,14 +7561,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -25566,4 +25989,1194 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21BC2329-6F8D-40DC-AA0F-7900E9C0A946}">
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="69" customWidth="1"/>
+    <col min="8" max="8" width="56.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2356</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2359</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2364</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2368</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2369</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2373</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2374</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2376</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>2378</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2388</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2391</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B19" t="s">
+        <v>992</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D19" t="s">
+        <v>993</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2396</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>515</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2398</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2399</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>515</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>611</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2405</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2407</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>611</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2411</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>611</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2416</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>611</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2417</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2419</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2420</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>611</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>515</v>
+      </c>
+      <c r="B26" t="s">
+        <v>398</v>
+      </c>
+      <c r="C26" t="s">
+        <v>399</v>
+      </c>
+      <c r="D26" t="s">
+        <v>400</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2421</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>611</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>515</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2422</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>611</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>515</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2425</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>611</v>
+      </c>
+      <c r="H28" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>515</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>611</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>515</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>611</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>515</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>611</v>
+      </c>
+      <c r="H31" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>515</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2440</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2441</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>515</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2443</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2444</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2445</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>515</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2447</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>515</v>
+      </c>
+      <c r="B35" t="s">
+        <v>535</v>
+      </c>
+      <c r="D35" t="s">
+        <v>536</v>
+      </c>
+      <c r="E35" t="s">
+        <v>537</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>515</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C36" t="s">
+        <v>532</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>515</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2453</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>515</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C38" t="s">
+        <v>532</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2456</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2457</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>515</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2458</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>515</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2462</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>515</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C41" t="s">
+        <v>532</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2465</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2466</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>515</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2467</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E42" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>515</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2471</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>515</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2473</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2475</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>515</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2477</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>515</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2487</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B48" t="s">
+        <v>525</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2490</v>
+      </c>
+      <c r="D48" t="s">
+        <v>526</v>
+      </c>
+      <c r="E48" t="s">
+        <v>527</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630CDB33-6C8D-4196-A705-AFE96BB34C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CC30DA-1EA9-4B0E-8EC1-7A305166B14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Nr6_April13" sheetId="7" r:id="rId7"/>
     <sheet name="Rättningar_April16" sheetId="8" r:id="rId8"/>
     <sheet name="Nr7_Juni1" sheetId="9" r:id="rId9"/>
+    <sheet name="Nr8" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5853" uniqueCount="2491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6064" uniqueCount="2579">
   <si>
     <t>Imprint</t>
   </si>
@@ -7506,6 +7507,270 @@
   </si>
   <si>
     <t>0947-031X</t>
+  </si>
+  <si>
+    <t>Pensoft</t>
+  </si>
+  <si>
+    <t>3033-2117</t>
+  </si>
+  <si>
+    <t>Advances in Pollinator Research</t>
+  </si>
+  <si>
+    <t>https://apr.pensoft.net/</t>
+  </si>
+  <si>
+    <t>3061-0214</t>
+  </si>
+  <si>
+    <t>3061-0206</t>
+  </si>
+  <si>
+    <t>The Annals of the Natural History Museum Vienna</t>
+  </si>
+  <si>
+    <t>https://anhmw.pensoft.net/</t>
+  </si>
+  <si>
+    <t>2710-298X</t>
+  </si>
+  <si>
+    <t>1026-4949</t>
+  </si>
+  <si>
+    <t>Biosystematics and Ecology</t>
+  </si>
+  <si>
+    <t>https://biosystecol.oeaw.ac.at/</t>
+  </si>
+  <si>
+    <t>2667-9809</t>
+  </si>
+  <si>
+    <t>Caucasiana</t>
+  </si>
+  <si>
+    <t>https://caucasiana.pensoft.net/</t>
+  </si>
+  <si>
+    <t>1314-0027</t>
+  </si>
+  <si>
+    <t>1310-7771</t>
+  </si>
+  <si>
+    <t>Phytologia Balcanica</t>
+  </si>
+  <si>
+    <t>https://phytolbalcan.arphahub.com/</t>
+  </si>
+  <si>
+    <t>2367-8518</t>
+  </si>
+  <si>
+    <t>2367-850X</t>
+  </si>
+  <si>
+    <t>Problems of Dental Medicine</t>
+  </si>
+  <si>
+    <t>https://pdm.pensoft.net/</t>
+  </si>
+  <si>
+    <t>2247-9902</t>
+  </si>
+  <si>
+    <t>1842-614X</t>
+  </si>
+  <si>
+    <t>The Scientific Annals of the Danube Delta Institute</t>
+  </si>
+  <si>
+    <t>https://saddi.pensoft.net/</t>
+  </si>
+  <si>
+    <t>1661-8726</t>
+  </si>
+  <si>
+    <t>https://sjg.pensoft.net/</t>
+  </si>
+  <si>
+    <t>1664-2376</t>
+  </si>
+  <si>
+    <t>https://sjp.pensoft.net/</t>
+  </si>
+  <si>
+    <t>2977-5884</t>
+  </si>
+  <si>
+    <t>BMJ Immunology</t>
+  </si>
+  <si>
+    <t>https://bmjimmunology.bmj.com/</t>
+  </si>
+  <si>
+    <t>2755-6670</t>
+  </si>
+  <si>
+    <t>Lifestyle Medicine Advances</t>
+  </si>
+  <si>
+    <t>https://lifestylemedicine.bmj.com/</t>
+  </si>
+  <si>
+    <t>3043-0429</t>
+  </si>
+  <si>
+    <t>Addiction &amp; Prevention</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/addictprev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3043-0259 </t>
+  </si>
+  <si>
+    <t>Archaeological Studies</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/archaeolstud</t>
+  </si>
+  <si>
+    <t>3043-100X</t>
+  </si>
+  <si>
+    <t>Breast Cancer Research and Care</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/bcrc</t>
+  </si>
+  <si>
+    <t>3042-8718</t>
+  </si>
+  <si>
+    <t>Crafts</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/crafts</t>
+  </si>
+  <si>
+    <t>3042-9315</t>
+  </si>
+  <si>
+    <t>Digital Health and Innovation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/dhi</t>
+  </si>
+  <si>
+    <t>3042-903X</t>
+  </si>
+  <si>
+    <t>Environmental Remediation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/environremediat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3043-0569 </t>
+  </si>
+  <si>
+    <t>Freshwater</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/freshwater</t>
+  </si>
+  <si>
+    <t>3042-9242</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/green</t>
+  </si>
+  <si>
+    <t>3042-9021</t>
+  </si>
+  <si>
+    <t>Industries</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/industries</t>
+  </si>
+  <si>
+    <t>3043-0348</t>
+  </si>
+  <si>
+    <t>Inflammation Journal</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/inflammj</t>
+  </si>
+  <si>
+    <t>3042-8890</t>
+  </si>
+  <si>
+    <t>International Journal of Medical Devices</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-8424 </t>
+  </si>
+  <si>
+    <t>Journal of Genome Biotechnology and Genetics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jgbg</t>
+  </si>
+  <si>
+    <t>3043-0097</t>
+  </si>
+  <si>
+    <t>Journal of Superintelligence</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/superintelligence</t>
+  </si>
+  <si>
+    <t>3042-9323</t>
+  </si>
+  <si>
+    <t>Pandemics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/pandemics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3043-002X </t>
+  </si>
+  <si>
+    <t>Smart Fisheries</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/smartfish</t>
+  </si>
+  <si>
+    <t>3042-9617</t>
+  </si>
+  <si>
+    <t>Welding</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/welding</t>
+  </si>
+  <si>
+    <t>3120-4732</t>
+  </si>
+  <si>
+    <t>European Radiology Cardiovascular and Thoracic</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/journal/44449</t>
   </si>
 </sst>
 </file>
@@ -18634,6 +18899,707 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D55FBCA-8A72-4BD8-8630-1FBB1C892F20}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2492</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2493</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2497</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2501</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2504</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2508</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2509</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2512</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2513</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2515</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2516</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2517</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B10" t="s">
+        <v>888</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D10" t="s">
+        <v>889</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2521</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2523</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2524</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2526</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2527</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2529</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2531</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2532</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2533</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2538</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2542</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2545</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2547</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2548</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2550</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2551</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2552</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2554</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2557</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2563</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2566</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2569</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2572</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2573</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2575</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>634</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1D323B-A6AD-4330-BC48-B16F75806926}">
   <dimension ref="A1:H54"/>

--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CC30DA-1EA9-4B0E-8EC1-7A305166B14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A1061D-4D90-4B52-B433-CE332785A7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Rättningar_April16" sheetId="8" r:id="rId8"/>
     <sheet name="Nr7_Juni1" sheetId="9" r:id="rId9"/>
     <sheet name="Nr8" sheetId="10" r:id="rId10"/>
+    <sheet name="Nr9" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6064" uniqueCount="2579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6079" uniqueCount="2582">
   <si>
     <t>Imprint</t>
   </si>
@@ -7771,6 +7772,15 @@
   </si>
   <si>
     <t>https://link.springer.com/journal/44449</t>
+  </si>
+  <si>
+    <t>1535-4989</t>
+  </si>
+  <si>
+    <t>American Journal of Respiratory Cell and Molecular Biology</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/ajrcmb</t>
   </si>
 </sst>
 </file>
@@ -19600,6 +19610,68 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920D3B5F-E1A6-4E4C-A9C8-3CA0D80B5344}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="58.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2579</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1D323B-A6AD-4330-BC48-B16F75806926}">
   <dimension ref="A1:H54"/>

--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A1061D-4D90-4B52-B433-CE332785A7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37571098-8783-4A56-9D7B-7E753EFC8C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Nr7_Juni1" sheetId="9" r:id="rId9"/>
     <sheet name="Nr8" sheetId="10" r:id="rId10"/>
     <sheet name="Nr9" sheetId="11" r:id="rId11"/>
+    <sheet name="Nr10" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6079" uniqueCount="2582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6115" uniqueCount="2597">
   <si>
     <t>Imprint</t>
   </si>
@@ -7781,6 +7782,51 @@
   </si>
   <si>
     <t>https://academic.oup.com/ajrcmb</t>
+  </si>
+  <si>
+    <t>3049-7523</t>
+  </si>
+  <si>
+    <t>Dialogues in Management</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/DMA</t>
+  </si>
+  <si>
+    <t>2755-5666</t>
+  </si>
+  <si>
+    <t>2755-6662</t>
+  </si>
+  <si>
+    <t>Translational Data Science for Social Impact</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/TDS</t>
+  </si>
+  <si>
+    <t>JMIR</t>
+  </si>
+  <si>
+    <t>rättat till license options till CC-BY</t>
+  </si>
+  <si>
+    <t>Elsevier och Cell Press</t>
+  </si>
+  <si>
+    <t>1889-1837</t>
+  </si>
+  <si>
+    <t>1989-4805</t>
+  </si>
+  <si>
+    <t>Hipertensión y Riesgo Vascular</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/hipertension-y-riesgo-vascular</t>
+  </si>
+  <si>
+    <t>Abeni har rättat issn, print och elektroniskt var ofta omkastat tidigare</t>
   </si>
 </sst>
 </file>
@@ -7853,11 +7899,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19672,6 +19719,142 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFCD008-D805-448F-8E15-F9F0B8B0EAC4}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2583</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2594</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1D323B-A6AD-4330-BC48-B16F75806926}">
   <dimension ref="A1:H54"/>
